--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-work-soc-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-work-soc-score-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3387" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3387" uniqueCount="548">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:28:06+00:00</t>
+    <t>2026-10-21T09:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1381,6 +1381,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -7406,7 +7410,7 @@
         <v>435</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>436</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
@@ -7415,10 +7419,10 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -7429,10 +7433,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7458,10 +7462,10 @@
         <v>432</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7512,7 +7516,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7524,7 +7528,7 @@
         <v>435</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>436</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
@@ -7533,10 +7537,10 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7547,10 +7551,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7576,16 +7580,16 @@
         <v>182</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7613,10 +7617,10 @@
         <v>117</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7634,7 +7638,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7652,10 +7656,10 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>369</v>
@@ -7669,10 +7673,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7698,16 +7702,16 @@
         <v>182</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7735,10 +7739,10 @@
         <v>270</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7756,7 +7760,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7774,10 +7778,10 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>369</v>
@@ -7791,10 +7795,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7817,17 +7821,17 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7876,7 +7880,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7900,7 +7904,7 @@
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -7911,10 +7915,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7940,10 +7944,10 @@
         <v>160</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7994,7 +7998,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8015,10 +8019,10 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
@@ -8029,10 +8033,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8055,16 +8059,16 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8114,7 +8118,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8135,10 +8139,10 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
@@ -8149,10 +8153,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8175,16 +8179,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8234,7 +8238,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8255,10 +8259,10 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8269,10 +8273,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8280,10 +8284,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -8298,16 +8302,16 @@
         <v>416</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8344,7 +8348,7 @@
         <v>21</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
@@ -8354,7 +8358,7 @@
         <v>314</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8375,10 +8379,10 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8389,10 +8393,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8507,10 +8511,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8627,10 +8631,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8749,10 +8753,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8778,13 +8782,13 @@
         <v>182</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>268</v>
@@ -8836,7 +8840,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>93</v>
@@ -8854,7 +8858,7 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>275</v>
@@ -8871,10 +8875,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8900,13 +8904,13 @@
         <v>340</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>344</v>
@@ -8958,7 +8962,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8976,7 +8980,7 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>347</v>
@@ -8993,10 +8997,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9022,13 +9026,13 @@
         <v>182</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>354</v>
@@ -9080,7 +9084,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9115,10 +9119,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9202,7 +9206,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9237,10 +9241,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9266,10 +9270,10 @@
         <v>21</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>419</v>
@@ -9324,7 +9328,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9359,13 +9363,13 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>21</v>
@@ -9390,16 +9394,16 @@
         <v>416</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9448,7 +9452,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9469,10 +9473,10 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>21</v>
@@ -9483,10 +9487,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9601,10 +9605,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9721,10 +9725,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9843,10 +9847,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9872,13 +9876,13 @@
         <v>182</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>268</v>
@@ -9891,7 +9895,7 @@
         <v>21</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>21</v>
@@ -9930,7 +9934,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>93</v>
@@ -9948,7 +9952,7 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>275</v>
@@ -9965,10 +9969,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9991,16 +9995,16 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M66" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>344</v>
@@ -10052,7 +10056,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10070,7 +10074,7 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>347</v>
@@ -10087,10 +10091,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10116,13 +10120,13 @@
         <v>182</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>354</v>
@@ -10174,7 +10178,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10209,10 +10213,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10296,7 +10300,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10331,10 +10335,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10360,10 +10364,10 @@
         <v>83</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>419</v>
@@ -10418,7 +10422,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10453,13 +10457,13 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>21</v>
@@ -10484,16 +10488,16 @@
         <v>416</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -10542,7 +10546,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10563,10 +10567,10 @@
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>21</v>
@@ -10577,10 +10581,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10695,10 +10699,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10815,10 +10819,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10937,10 +10941,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10966,13 +10970,13 @@
         <v>182</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>268</v>
@@ -10985,7 +10989,7 @@
         <v>21</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>21</v>
@@ -11024,7 +11028,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>93</v>
@@ -11042,7 +11046,7 @@
         <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>275</v>
@@ -11059,10 +11063,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11085,16 +11089,16 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O75" t="s" s="2">
         <v>344</v>
@@ -11146,7 +11150,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11164,7 +11168,7 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>347</v>
@@ -11181,10 +11185,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11210,13 +11214,13 @@
         <v>182</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O76" t="s" s="2">
         <v>354</v>
@@ -11268,7 +11272,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11303,10 +11307,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11390,7 +11394,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11425,10 +11429,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11454,10 +11458,10 @@
         <v>83</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>419</v>
@@ -11512,7 +11516,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11547,13 +11551,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>21</v>
@@ -11578,16 +11582,16 @@
         <v>416</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -11636,7 +11640,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11657,10 +11661,10 @@
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>21</v>
@@ -11671,10 +11675,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11789,10 +11793,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11909,10 +11913,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12031,10 +12035,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12060,13 +12064,13 @@
         <v>182</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O83" t="s" s="2">
         <v>268</v>
@@ -12079,7 +12083,7 @@
         <v>21</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>21</v>
@@ -12118,7 +12122,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>93</v>
@@ -12136,7 +12140,7 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>275</v>
@@ -12153,10 +12157,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12179,16 +12183,16 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M84" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O84" t="s" s="2">
         <v>344</v>
@@ -12240,7 +12244,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12258,7 +12262,7 @@
         <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>347</v>
@@ -12275,10 +12279,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12304,13 +12308,13 @@
         <v>182</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O85" t="s" s="2">
         <v>354</v>
@@ -12362,7 +12366,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12397,10 +12401,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12484,7 +12488,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12519,10 +12523,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12548,10 +12552,10 @@
         <v>83</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>419</v>
@@ -12606,7 +12610,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
